--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134849228</v>
+        <v>135495962</v>
       </c>
       <c r="B2" t="n">
-        <v>99195</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Solamm, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497014</v>
+        <v>497182</v>
       </c>
       <c r="R2" t="n">
-        <v>6831015</v>
+        <v>6831085</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,79 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134849246</v>
+        <v>135497733</v>
       </c>
       <c r="B3" t="n">
-        <v>99195</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solamm, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497017</v>
+        <v>497137</v>
       </c>
       <c r="R3" t="n">
-        <v>6831014</v>
+        <v>6831200</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +851,4090 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135494825</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497070</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6831043</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135494875</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6831034</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135494956</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135494966</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497105</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6831052</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135495055</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6831053</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135495737</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497149</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831086</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135496306</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497199</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6831051</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135494584</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>497025</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831044</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135496200</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497188</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6831073</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135496859</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Solamm, Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497263</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6831131</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135498379</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497052</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135495243</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90997</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497111</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6831059</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135497609</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90997</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497175</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6831197</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135495796</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497185</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6831081</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135495970</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497202</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831112</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135497047</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>497234</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831165</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135493876</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496910</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6830981</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135493913</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496935</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6830980</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135494106</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496986</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6831007</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135495000</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135495403</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>497111</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6831081</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135495610</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>497144</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831086</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135496547</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>497236</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831077</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135497671</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>497175</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6831197</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135497740</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>497073</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6831196</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135497844</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>497050</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6831160</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135497894</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>497137</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6831200</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135498475</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>497052</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6831200</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135495098</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>497110</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6831069</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135495307</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>497115</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6831093</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135495743</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>497173</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6831084</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135495833</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>497182</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6831085</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134849228</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>497014</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6831015</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Jonas Karlsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>Jonas Karlsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134849246</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>497017</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6831014</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135494624</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>497026</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6831050</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135494666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>496935</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6830980</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135498596</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>496927</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6830908</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tre blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135498654</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>496937</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6830904</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tre blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135494002</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>496973</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6831014</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135495080</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135496523</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>497253</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6831099</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497733</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494875</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494956</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494966</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495055</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495737</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496306</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494584</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496200</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496859</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498379</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495243</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497609</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495796</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495970</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497047</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493876</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493913</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494106</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495000</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495403</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495610</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496547</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497671</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497740</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497844</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497894</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498475</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495098</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495307</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495743</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3979,6 +4149,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495833</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4094,6 +4269,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849228</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4209,6 +4389,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849246</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4306,6 +4491,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494624</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4412,6 +4602,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494666</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4528,6 +4723,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498596</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4644,6 +4844,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498654</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4741,6 +4946,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494002</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4838,6 +5048,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495080</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4935,8 +5150,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495962</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135497733</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135494825</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135494875</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135494956</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135494966</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495055</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495737</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135496306</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135494584</v>
       </c>
       <c r="B11" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135496200</v>
       </c>
       <c r="B12" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135496859</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135498379</v>
       </c>
       <c r="B14" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495243</v>
       </c>
       <c r="B15" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135497609</v>
       </c>
       <c r="B16" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495796</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495970</v>
       </c>
       <c r="B18" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135497047</v>
       </c>
       <c r="B19" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135493876</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135493913</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>135494106</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>135495000</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135495403</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>135495610</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>135496547</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>135497671</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135497740</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>135497844</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135497894</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>135498475</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>135495098</v>
       </c>
       <c r="B32" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>135495307</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>135495743</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>135495833</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>134849228</v>
       </c>
       <c r="B36" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>134849246</v>
       </c>
       <c r="B37" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135494624</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>135494666</v>
       </c>
       <c r="B39" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135498596</v>
       </c>
       <c r="B40" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>135498654</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>135494002</v>
       </c>
       <c r="B42" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>135495080</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135496523</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495962</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135497733</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135494825</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135494875</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135494956</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135494966</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135495055</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135495737</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135496306</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135494584</v>
       </c>
       <c r="B11" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135496200</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135496859</v>
       </c>
       <c r="B13" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135498379</v>
       </c>
       <c r="B14" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495243</v>
       </c>
       <c r="B15" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135497609</v>
       </c>
       <c r="B16" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495796</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495970</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135497047</v>
       </c>
       <c r="B19" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135493876</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135493913</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>135494106</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>135495000</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>135495403</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>135495610</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>135496547</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>135497671</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>135497740</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>135497844</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135497894</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>135498475</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>135495098</v>
       </c>
       <c r="B32" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>135495307</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>135495743</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>134849228</v>
       </c>
       <c r="B36" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>134849246</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135494624</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>135494666</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135498596</v>
       </c>
       <c r="B40" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>135498654</v>
       </c>
       <c r="B41" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>135494002</v>
       </c>
       <c r="B42" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>135495080</v>
       </c>
       <c r="B43" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135496523</v>
       </c>
       <c r="B44" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134849228</v>
+        <v>135495962</v>
       </c>
       <c r="B2" t="n">
-        <v>99269</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Solamm, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497014</v>
+        <v>497182</v>
       </c>
       <c r="R2" t="n">
-        <v>6831015</v>
+        <v>6831085</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,84 +759,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134849228</t>
+          <t>https://artportalen.se/Sighting/135495962</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134849246</v>
+        <v>135497733</v>
       </c>
       <c r="B3" t="n">
-        <v>99269</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solamm, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497017</v>
+        <v>497137</v>
       </c>
       <c r="R3" t="n">
-        <v>6831014</v>
+        <v>6831200</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,25 +861,4298 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135497733</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135494825</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497070</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6831043</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494825</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135494875</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6831034</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494875</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135494956</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494956</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135494966</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497105</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6831052</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494966</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135495055</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6831053</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495055</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135495737</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497149</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831086</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495737</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135496306</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>497199</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6831051</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496306</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135494584</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>497025</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831044</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494584</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135496200</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497188</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6831073</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496200</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135496859</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Solamm, Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497263</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6831131</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496859</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135498379</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497052</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498379</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135495243</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91069</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497111</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6831059</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495243</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135497609</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91069</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497175</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6831197</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497609</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135495796</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497185</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6831081</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495796</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135495970</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497202</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831112</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495970</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135497047</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>497234</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831165</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497047</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135493876</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496910</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6830981</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493876</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135493913</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496935</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6830980</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493913</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135494106</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496986</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6831007</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494106</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135495000</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135495403</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>497111</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6831081</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495403</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135495610</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>497144</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831086</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495610</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135496547</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>497236</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831077</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496547</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135497671</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>497175</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6831197</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497671</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135497740</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>497073</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6831196</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497740</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135497844</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>497050</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6831160</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497844</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135497894</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>497137</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6831200</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135497894</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135498475</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>497052</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6831200</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498475</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135495098</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>497110</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6831069</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495098</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135495307</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>497115</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6831093</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495307</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135495743</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>497173</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6831084</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495743</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135495833</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>497182</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6831085</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495833</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134849228</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>497014</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6831015</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849228</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134849246</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>497017</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6831014</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134849246</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135494624</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>497026</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6831050</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494624</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135494666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>496935</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6830980</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135498596</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>496927</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6830908</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tre blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498596</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135498654</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>496937</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6830904</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tre blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498654</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135494002</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>496973</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6831014</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135495080</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495080</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135496523</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>497253</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6831099</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135496523</t>
         </is>
       </c>
     </row>
@@ -922,6 +5160,47 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135495962</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135494584</v>
       </c>
       <c r="B11" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135496200</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135496859</v>
       </c>
       <c r="B13" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135498379</v>
       </c>
       <c r="B14" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135495243</v>
       </c>
       <c r="B15" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135497609</v>
       </c>
       <c r="B16" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135495796</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135495970</v>
       </c>
       <c r="B18" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135497047</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>135494624</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>135494666</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135498596</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>135498654</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 30892-2026 artfynd.xlsx
+++ b/artfynd/A 30892-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ44"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,48 +1598,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135494584</v>
+        <v>135891859</v>
       </c>
       <c r="B11" t="n">
-        <v>92229</v>
+        <v>79107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497025</v>
+        <v>496967</v>
       </c>
       <c r="R11" t="n">
-        <v>6831044</v>
+        <v>6830916</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1663,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,62 +1693,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494584</t>
+          <t>https://artportalen.se/Sighting/135891859</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135496200</v>
+        <v>135891860</v>
       </c>
       <c r="B12" t="n">
-        <v>92229</v>
+        <v>79107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497188</v>
+        <v>496962</v>
       </c>
       <c r="R12" t="n">
-        <v>6831073</v>
+        <v>6830917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1775,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,65 +1805,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135496200</t>
+          <t>https://artportalen.se/Sighting/135891860</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135496859</v>
+        <v>135891861</v>
       </c>
       <c r="B13" t="n">
-        <v>92229</v>
+        <v>79107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Solamm, Solamm, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497263</v>
+        <v>497004</v>
       </c>
       <c r="R13" t="n">
-        <v>6831131</v>
+        <v>6830882</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1887,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,65 +1917,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135496859</t>
+          <t>https://artportalen.se/Sighting/135891861</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135498379</v>
+        <v>135905879</v>
       </c>
       <c r="B14" t="n">
-        <v>92229</v>
+        <v>79107</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497052</v>
+        <v>496977</v>
       </c>
       <c r="R14" t="n">
-        <v>6831200</v>
+        <v>6830933</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1999,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,65 +2029,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135498379</t>
+          <t>https://artportalen.se/Sighting/135905879</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135495243</v>
+        <v>135494584</v>
       </c>
       <c r="B15" t="n">
-        <v>91071</v>
+        <v>92229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497111</v>
+        <v>497025</v>
       </c>
       <c r="R15" t="n">
-        <v>6831059</v>
+        <v>6831044</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,49 +2131,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495243</t>
+          <t>https://artportalen.se/Sighting/135494584</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135497609</v>
+        <v>135496200</v>
       </c>
       <c r="B16" t="n">
-        <v>91071</v>
+        <v>92229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497175</v>
+        <v>497188</v>
       </c>
       <c r="R16" t="n">
-        <v>6831197</v>
+        <v>6831073</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,54 +2244,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135497609</t>
+          <t>https://artportalen.se/Sighting/135496200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135495796</v>
+        <v>135496859</v>
       </c>
       <c r="B17" t="n">
-        <v>92103</v>
+        <v>92229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Solamm, Solamm, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497185</v>
+        <v>497263</v>
       </c>
       <c r="R17" t="n">
-        <v>6831081</v>
+        <v>6831131</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,65 +2335,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495796</t>
+          <t>https://artportalen.se/Sighting/135496859</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135495970</v>
+        <v>135498379</v>
       </c>
       <c r="B18" t="n">
-        <v>92103</v>
+        <v>92229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497202</v>
+        <v>497052</v>
       </c>
       <c r="R18" t="n">
-        <v>6831112</v>
+        <v>6831200</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,27 +2437,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495970</t>
+          <t>https://artportalen.se/Sighting/135498379</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135497047</v>
+        <v>135495243</v>
       </c>
       <c r="B19" t="n">
-        <v>92103</v>
+        <v>91071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,37 +2465,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497234</v>
+        <v>497111</v>
       </c>
       <c r="R19" t="n">
-        <v>6831165</v>
+        <v>6831059</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,65 +2539,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135497047</t>
+          <t>https://artportalen.se/Sighting/135495243</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135493876</v>
+        <v>135497609</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>91071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496910</v>
+        <v>497175</v>
       </c>
       <c r="R20" t="n">
-        <v>6830981</v>
+        <v>6831197</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,65 +2641,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493876</t>
+          <t>https://artportalen.se/Sighting/135497609</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135493913</v>
+        <v>135495796</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>92103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496935</v>
+        <v>497185</v>
       </c>
       <c r="R21" t="n">
-        <v>6830980</v>
+        <v>6831081</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2703,65 +2743,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493913</t>
+          <t>https://artportalen.se/Sighting/135495796</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135494106</v>
+        <v>135495970</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>92103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496986</v>
+        <v>497202</v>
       </c>
       <c r="R22" t="n">
-        <v>6831007</v>
+        <v>6831112</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,49 +2845,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494106</t>
+          <t>https://artportalen.se/Sighting/135495970</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135495000</v>
+        <v>135497047</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>92103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497102</v>
+        <v>497234</v>
       </c>
       <c r="R23" t="n">
-        <v>6831045</v>
+        <v>6831165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,54 +2958,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495000</t>
+          <t>https://artportalen.se/Sighting/135497047</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135495403</v>
+        <v>135891856</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>93347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497111</v>
+        <v>496914</v>
       </c>
       <c r="R24" t="n">
-        <v>6831081</v>
+        <v>6830980</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2989,12 +3029,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3009,65 +3059,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495403</t>
+          <t>https://artportalen.se/Sighting/135891856</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135495610</v>
+        <v>135905880</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>93347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497144</v>
+        <v>496973</v>
       </c>
       <c r="R25" t="n">
-        <v>6831086</v>
+        <v>6830929</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3091,12 +3141,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,65 +3171,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495610</t>
+          <t>https://artportalen.se/Sighting/135905880</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135496547</v>
+        <v>135905976</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>93347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497236</v>
+        <v>497105</v>
       </c>
       <c r="R26" t="n">
-        <v>6831077</v>
+        <v>6830981</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3193,12 +3253,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,65 +3283,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135496547</t>
+          <t>https://artportalen.se/Sighting/135905976</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135497671</v>
+        <v>135905977</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>93347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497175</v>
+        <v>497050</v>
       </c>
       <c r="R27" t="n">
-        <v>6831197</v>
+        <v>6830980</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3295,12 +3365,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3315,24 +3395,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135497671</t>
+          <t>https://artportalen.se/Sighting/135905977</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135497740</v>
+        <v>135493876</v>
       </c>
       <c r="B28" t="n">
         <v>79441</v>
@@ -3363,14 +3443,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497073</v>
+        <v>496910</v>
       </c>
       <c r="R28" t="n">
-        <v>6831196</v>
+        <v>6830981</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3428,13 +3508,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135497740</t>
+          <t>https://artportalen.se/Sighting/135493876</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135497844</v>
+        <v>135493913</v>
       </c>
       <c r="B29" t="n">
         <v>79441</v>
@@ -3465,14 +3545,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497050</v>
+        <v>496935</v>
       </c>
       <c r="R29" t="n">
-        <v>6831160</v>
+        <v>6830980</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3530,13 +3610,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135497844</t>
+          <t>https://artportalen.se/Sighting/135493913</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135497894</v>
+        <v>135494106</v>
       </c>
       <c r="B30" t="n">
         <v>79441</v>
@@ -3571,10 +3651,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497137</v>
+        <v>496986</v>
       </c>
       <c r="R30" t="n">
-        <v>6831200</v>
+        <v>6831007</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,13 +3712,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135497894</t>
+          <t>https://artportalen.se/Sighting/135494106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135498475</v>
+        <v>135495000</v>
       </c>
       <c r="B31" t="n">
         <v>79441</v>
@@ -3673,10 +3753,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497052</v>
+        <v>497102</v>
       </c>
       <c r="R31" t="n">
-        <v>6831200</v>
+        <v>6831045</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,54 +3814,54 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135498475</t>
+          <t>https://artportalen.se/Sighting/135495000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135495098</v>
+        <v>135495403</v>
       </c>
       <c r="B32" t="n">
-        <v>79198</v>
+        <v>79441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497110</v>
+        <v>497111</v>
       </c>
       <c r="R32" t="n">
-        <v>6831069</v>
+        <v>6831081</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3825,49 +3905,49 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495098</t>
+          <t>https://artportalen.se/Sighting/135495403</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135495307</v>
+        <v>135495610</v>
       </c>
       <c r="B33" t="n">
-        <v>80060</v>
+        <v>79441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3957,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497115</v>
+        <v>497144</v>
       </c>
       <c r="R33" t="n">
-        <v>6831093</v>
+        <v>6831086</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3938,38 +4018,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495307</t>
+          <t>https://artportalen.se/Sighting/135495610</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135495743</v>
+        <v>135496547</v>
       </c>
       <c r="B34" t="n">
-        <v>80060</v>
+        <v>79441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497173</v>
+        <v>497236</v>
       </c>
       <c r="R34" t="n">
-        <v>6831084</v>
+        <v>6831077</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4040,60 +4120,51 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495743</t>
+          <t>https://artportalen.se/Sighting/135496547</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135495833</v>
+        <v>135497671</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>79441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497182</v>
+        <v>497175</v>
       </c>
       <c r="R35" t="n">
-        <v>6831085</v>
+        <v>6831197</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,16 +4222,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495833</t>
+          <t>https://artportalen.se/Sighting/135497671</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134849228</v>
+        <v>135497740</v>
       </c>
       <c r="B36" t="n">
-        <v>99269</v>
+        <v>79441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4168,49 +4239,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Solamm, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497014</v>
+        <v>497073</v>
       </c>
       <c r="R36" t="n">
-        <v>6831015</v>
+        <v>6831196</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4234,17 +4293,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4253,34 +4307,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134849228</t>
+          <t>https://artportalen.se/Sighting/135497740</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134849246</v>
+        <v>135497844</v>
       </c>
       <c r="B37" t="n">
-        <v>99269</v>
+        <v>79441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4288,49 +4341,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Solamm, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497017</v>
+        <v>497050</v>
       </c>
       <c r="R37" t="n">
-        <v>6831014</v>
+        <v>6831160</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4354,17 +4395,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4373,34 +4409,33 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134849246</t>
+          <t>https://artportalen.se/Sighting/135497844</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135494624</v>
+        <v>135497894</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>79441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4408,21 +4443,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4432,10 +4467,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497026</v>
+        <v>497137</v>
       </c>
       <c r="R38" t="n">
-        <v>6831050</v>
+        <v>6831200</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,16 +4528,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494624</t>
+          <t>https://artportalen.se/Sighting/135497894</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135494666</v>
+        <v>135498475</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>79441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4510,46 +4545,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Dlr</t>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496935</v>
+        <v>497052</v>
       </c>
       <c r="R39" t="n">
-        <v>6830980</v>
+        <v>6831200</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4593,27 +4619,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494666</t>
+          <t>https://artportalen.se/Sighting/135498475</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135498596</v>
+        <v>135905876</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>79441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,51 +4647,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496927</v>
+        <v>496913</v>
       </c>
       <c r="R40" t="n">
-        <v>6830908</v>
+        <v>6830975</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4689,17 +4701,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Tre blommande exemplar.</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4714,27 +4731,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135498596</t>
+          <t>https://artportalen.se/Sighting/135905876</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135498654</v>
+        <v>135905884</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>79441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4742,51 +4759,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496937</v>
+        <v>496996</v>
       </c>
       <c r="R41" t="n">
-        <v>6830904</v>
+        <v>6830912</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4810,17 +4813,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Tre blommande exemplar.</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,27 +4843,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135498654</t>
+          <t>https://artportalen.se/Sighting/135905884</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135494002</v>
+        <v>135495098</v>
       </c>
       <c r="B42" t="n">
-        <v>79199</v>
+        <v>79198</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4863,37 +4871,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496973</v>
+        <v>497110</v>
       </c>
       <c r="R42" t="n">
-        <v>6831014</v>
+        <v>6831069</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4937,27 +4945,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494002</t>
+          <t>https://artportalen.se/Sighting/135495098</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135495080</v>
+        <v>135891939</v>
       </c>
       <c r="B43" t="n">
-        <v>79199</v>
+        <v>79198</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4965,37 +4973,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497102</v>
+        <v>497109</v>
       </c>
       <c r="R43" t="n">
-        <v>6831045</v>
+        <v>6830957</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5019,12 +5027,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5039,27 +5057,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135495080</t>
+          <t>https://artportalen.se/Sighting/135891939</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135496523</v>
+        <v>135495307</v>
       </c>
       <c r="B44" t="n">
-        <v>79199</v>
+        <v>80060</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5067,21 +5085,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5091,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497253</v>
+        <v>497115</v>
       </c>
       <c r="R44" t="n">
-        <v>6831099</v>
+        <v>6831093</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5151,6 +5169,2583 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495307</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135495743</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>497173</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6831084</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495743</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135891857</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>496917</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6830982</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891857</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135891863</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>496960</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6830928</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891863</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135905878</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>496977</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6830926</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905878</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135495833</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>497182</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6831085</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495833</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135891855</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>496892</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6830965</v>
+      </c>
+      <c r="S50" t="n">
+        <v>12</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891855</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135891858</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>496917</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6830982</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891858</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135905877</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>496956</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6830954</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905877</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135905975</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>497109</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6830986</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905975</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135905978</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>497024</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6830975</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905978</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135905979</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>496969</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6830982</v>
+      </c>
+      <c r="S55" t="n">
+        <v>6</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905979</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135905882</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99193</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>496988</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6830930</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905882</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135905883</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99193</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>496992</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6830930</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Alma Strandanger , Malte Lindberg, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905883</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134849228</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>497014</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6831015</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849228</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134849246</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Solamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>497017</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6831014</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Återfunnen under Orsa Besparingsskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jonas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849246</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135494624</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>497026</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6831050</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494624</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135494666</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>496935</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6830980</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494666</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135498596</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>496927</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6830908</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Tre blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498596</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135498654</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>496937</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6830904</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Tre blommande exemplar.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135498654</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135891854</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>496897</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6831032</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135891854</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135494002</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>496973</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6831014</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494002</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135495080</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hötjärnkojan, Hötjärnkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>497102</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6831045</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135495080</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135496523</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>497253</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6831099</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135496523</t>
         </is>
@@ -5201,6 +7796,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
